--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,9 +802,129 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136924113</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106494</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väster Bogestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566227</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6515776</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anette Källman, Mirjam Ideström, Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136924113</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anette Källman, Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström, Anette Källman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström, Anette Källman</t>
+          <t>Anette Källman, Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -718,11 +718,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -842,11 +838,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32070-2026 artfynd.xlsx
+++ b/artfynd/A 32070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902981</v>
       </c>
       <c r="B2" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136924113</v>
       </c>
       <c r="B3" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
